--- a/data/seed/portfolio/L-2025-3085/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-3085/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I177"/>
+  <dimension ref="A1:I133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -559,32 +559,32 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>8194000</v>
+        <v>23490000</v>
       </c>
       <c r="D10" s="2" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Angren Dori-Darmon AJ</t>
+          <t>Namangan Meva Eksport XK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>284729090</t>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000823744221001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №184/26</t>
+          <t>Предоплата за материалы по договору №45/26</t>
         </is>
       </c>
     </row>
@@ -600,32 +600,32 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>9410000</v>
+        <v>85591000</v>
       </c>
       <c r="D11" s="2" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sharq Dori-Darmon AJ</t>
+          <t>Namangan Meva Eksport XK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>303333044</t>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000343586109001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №30/26</t>
+          <t>Оплата за сырье по договору №122/26 от 02.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -642,38 +642,38 @@
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>3418000</v>
+        <v>9687000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Farg'ona Tikuv MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>204408221</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000626701482001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6561</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7491</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -683,31 +683,31 @@
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>3172000</v>
+        <v>29418000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8596 03.07.2026, QQS bilan</t>
+          <t>Shartnoma №114/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -724,21 +724,21 @@
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>17893000</v>
+        <v>15120000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yangi Hayot Savdo MChJ</t>
+          <t>Farg'ona Tikuv MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>333044082</t>
+          <t>204408221</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000116267014001</t>
+          <t>20208000626701482001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, H/F №9502 06.07.2026, QQS BILAN</t>
+          <t>Mahsulot uchun to'lov, shartnoma №169/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -765,31 +765,31 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>8044000</v>
+        <v>13968000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №4/26, QQS 12%</t>
+          <t>Shartnoma №193/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -804,33 +804,33 @@
           <t>106</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n">
-        <v>5358000</v>
-      </c>
+      <c r="C16" s="2" t="n">
+        <v>12935000</v>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Samarqand Savdo MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>348507161</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000861911625001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7995</t>
+          <t>Оплата за сырье по договору №177/26 от 06.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -845,23 +845,18 @@
           <t>107</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n">
-        <v>3465000</v>
-      </c>
+      <c r="C17" s="2" t="n">
+        <v>17882000</v>
+      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>284201097</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -871,14 +866,14 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №4757 за поставленный товар</t>
+          <t>Перечисление заработной платы за июнь 2026 г. согласно реестру №9045</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -888,38 +883,38 @@
       </c>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n">
-        <v>2107000</v>
+        <v>4965000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №132/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №59/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -928,39 +923,39 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>3370000</v>
+        <v>2330000</v>
       </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sharq Dori-Darmon AJ</t>
+          <t>Namangan Qurilish XK</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>303333044</t>
+          <t>399761229</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000343586109001</t>
+          <t>20208000515269130001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №210/26</t>
+          <t>Ijara haqi iyul oyi uchun, shartn. №6/25</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -969,39 +964,39 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>4155000</v>
+        <v>3797000</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zafar Tikuv MChJ</t>
+          <t>Xiva Trans Servis AJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>359976122</t>
+          <t>359373150</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000651526913001</t>
+          <t>20208000258037213001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №206/26, QQS bilan</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №247/26</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1010,39 +1005,39 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>6350000</v>
+        <v>2438000</v>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sharq Dori-Darmon AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>303333044</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000343586109001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №292/26</t>
+          <t>Iyun oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1051,34 +1046,39 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>17882000</v>
+        <v>2438000</v>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
+          <t>Jismoniy shaxslar daromad solig'i iyun 2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1087,39 +1087,39 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>2330000</v>
+        <v>8677000</v>
       </c>
       <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Farovon Qurilish MChJ</t>
+          <t>Yulduz Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>263920056</t>
+          <t>383083072</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000047556299001</t>
+          <t>20208000924600813001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>BINO IJARASI UCHUN TO'LOV IYUL</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №161/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1127,23 +1127,18 @@
           <t>114</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n">
-        <v>9201000</v>
-      </c>
+      <c r="C24" s="2" t="n">
+        <v>17200000</v>
+      </c>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>284201097</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-3085)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>16307000369122889417</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1153,14 +1148,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №105/26, QQS 12%</t>
+          <t>Kredit shartnomasi L-2025-3085 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1169,39 +1164,39 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>17178000</v>
+        <v>13228000</v>
       </c>
       <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zafar Tikuv MChJ</t>
+          <t>Namangan Meva Eksport XK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>359976122</t>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000651526913001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №258/26</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №9253</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1209,40 +1204,40 @@
           <t>116</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n">
-        <v>3386000</v>
-      </c>
+      <c r="C26" s="2" t="n">
+        <v>3682000</v>
+      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Namangan Meva Eksport XK</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №4718 10.07.2026, QQS bilan</t>
+          <t>Предоплата за материалы по договору №285/26</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1250,40 +1245,40 @@
           <t>117</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n">
-        <v>2747000</v>
-      </c>
-      <c r="D27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n">
+        <v>20320000</v>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Marg'ilon Agro AJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>387593731</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000002580372001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №253/26</t>
+          <t>SHARTNOMA №138/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1293,38 +1288,38 @@
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>1953000</v>
+        <v>17541000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Andijon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>333470704</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000763103622001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Shartnoma №173/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №159/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1332,23 +1327,23 @@
           <t>119</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>6190000</v>
-      </c>
-      <c r="D29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n">
+        <v>4115000</v>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sharq Dori-Darmon AJ</t>
+          <t>Kamalak Sut Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>303333044</t>
+          <t>371839625</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000343586109001</t>
+          <t>20208000141915324001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1358,14 +1353,14 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №234/26, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №133/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1374,39 +1369,39 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>9706000</v>
+        <v>7963000</v>
       </c>
       <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sharq Dori-Darmon AJ</t>
+          <t>Xiva Trans Servis AJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>303333044</t>
+          <t>359373150</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000343586109001</t>
+          <t>20208000258037213001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №239/26</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №79/26</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1416,38 +1411,38 @@
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n">
-        <v>10706000</v>
+        <v>111312000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Yangi Hayot Savdo MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>333044082</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000116267014001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Shartnoma №69/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3817</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1455,40 +1450,40 @@
           <t>122</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>2438000</v>
-      </c>
-      <c r="D32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n">
+        <v>8620000</v>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ijtimoiy soliq</t>
+          <t>Предоплата за товар по договору №215/26 от 21.07.2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1497,7 +1492,7 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>2438000</v>
+        <v>3846000</v>
       </c>
       <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
@@ -1522,14 +1517,14 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i iyun 2026</t>
+          <t>QQS iyun 2026 uchun</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1537,40 +1532,40 @@
           <t>124</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n">
-        <v>2226000</v>
-      </c>
+      <c r="C34" s="2" t="n">
+        <v>5639000</v>
+      </c>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Yangi Hayot Savdo MChJ</t>
+          <t>Xiva Trans Servis AJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>333044082</t>
+          <t>359373150</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000116267014001</t>
+          <t>20208000258037213001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №755 15.07.2026, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №4558</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1579,34 +1574,39 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>17200000</v>
+        <v>1456000</v>
       </c>
       <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-3085)</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>16307000369122889417</t>
+          <t>20208000436392005001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-3085 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>ELEKTR ENERGIYASI UCHUN TO'LOV</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1614,23 +1614,23 @@
           <t>126</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>45245000</v>
-      </c>
-      <c r="D36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n">
+        <v>26415000</v>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mehnat Oziq-ovqat Savdo MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>264166099</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000374631289001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1640,14 +1640,14 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №34/26</t>
+          <t>Оплата за продукцию по договору №50/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1657,38 +1657,38 @@
       </c>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n">
-        <v>4522000</v>
+        <v>15960000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №6125</t>
+          <t>Mahsulot uchun to'lov, shartn. №55/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1696,40 +1696,40 @@
           <t>128</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>3656000</v>
-      </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n">
+        <v>14709000</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Marg'ilon Agro AJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>387593731</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000002580372001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №7180</t>
+          <t>Оплата за товар по с/ф №7267 от 27.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1739,38 +1739,38 @@
       </c>
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="n">
-        <v>5381000</v>
+        <v>11863000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2955 20.07.2026, QQS bilan</t>
+          <t>Shartnoma №297/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1779,39 +1779,39 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>35079000</v>
+        <v>15206000</v>
       </c>
       <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Angren Dori-Darmon AJ</t>
+          <t>Namangan Meva Eksport XK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>284729090</t>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000823744221001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №33/26</t>
+          <t>Оплата за товары согласно счет-фактуре №7261</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1819,40 +1819,40 @@
           <t>131</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n">
-        <v>2157000</v>
-      </c>
+      <c r="C41" s="2" t="n">
+        <v>98878000</v>
+      </c>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Namangan Meva Eksport XK</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Shartnoma №69/26 bo'yicha oldindan to'lov</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №99/26</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1862,38 +1862,38 @@
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>5302000</v>
+        <v>6359000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Omad Sut MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>376718396</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000581419153001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Shartnoma №147/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №138/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1903,38 +1903,38 @@
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>2404000</v>
+        <v>10107000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Yangi Hayot Savdo MChJ</t>
+          <t>Oqtosh Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>333044082</t>
+          <t>202093836</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000116267014001</t>
+          <t>20208000124627509001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5488</t>
+          <t>Оплата по счет-фактуре №6402 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1943,39 +1943,34 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>5988000</v>
+        <v>300000</v>
       </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sharq Dori-Darmon AJ</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>303333044</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000343586109001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №226/26</t>
+          <t>Hisob-kassa xizmati uchun haq</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,40 +1978,40 @@
           <t>135</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n">
-        <v>8733000</v>
-      </c>
-      <c r="D45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n">
+        <v>11748000</v>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>213841337</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000617055929001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №43/26, QQS bilan</t>
+          <t>Shartnoma №51/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2025,39 +2020,39 @@
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>3824000</v>
+        <v>31690000</v>
       </c>
       <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Xiva Trans Servis AJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>359373150</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000258037213001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
+          <t>Оплата за товары согласно счет-фактуре №405</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2065,40 +2060,40 @@
           <t>137</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n">
-        <v>58388000</v>
-      </c>
+      <c r="C47" s="2" t="n">
+        <v>67815000</v>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Namangan Meva Eksport XK</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8202</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №226/26</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2108,38 +2103,38 @@
       </c>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n">
-        <v>7262000</v>
+        <v>5068000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Yangi Hayot Savdo MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>333044082</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000116267014001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №8321 за поставленный товар</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9401 06.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2148,39 +2143,39 @@
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>1456000</v>
+        <v>12512000</v>
       </c>
       <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Namangan Meva Eksport XK</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000855050926001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №288/26</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2188,23 +2183,18 @@
           <t>140</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n">
-        <v>125519000</v>
-      </c>
+      <c r="C50" s="2" t="n">
+        <v>18677000</v>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>284201097</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2214,14 +2204,14 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Shartnoma №160/26 boyicha oldindan to'lov</t>
+          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2231,38 +2221,38 @@
       </c>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n">
-        <v>13856000</v>
+        <v>15777000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №36/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1866</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2272,38 +2262,38 @@
       </c>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="n">
-        <v>2919000</v>
+        <v>10905000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Chust Tikuv MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>365334707</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000447631036001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5666</t>
+          <t>Оплата за продукцию по договору №190/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2313,38 +2303,38 @@
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>2087000</v>
+        <v>7507000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Zafar Moy MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>233020938</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000661246275001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Shartnoma №192/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4223 07.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2352,40 +2342,40 @@
           <t>144</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n">
-        <v>2407000</v>
-      </c>
-      <c r="D54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n">
+        <v>6016000</v>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Chust Tur Servis XK</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>338830830</t>
+          <t>272909008</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000209246008001</t>
+          <t>20208000374422121001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №97/26, QQS bilan</t>
+          <t>Предоплата за товар по дог. №178/26 от 07.08.2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2394,39 +2384,39 @@
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>3566000</v>
+        <v>2433000</v>
       </c>
       <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Angren Dori-Darmon AJ</t>
+          <t>Namangan Qurilish XK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>284729090</t>
+          <t>399761229</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000823744221001</t>
+          <t>20208000515269130001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №3370</t>
+          <t>Bino ijarasi uchun to'lov avgust</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2434,23 +2424,23 @@
           <t>146</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n">
-        <v>26410000</v>
-      </c>
-      <c r="D56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n">
+        <v>37586000</v>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sharq Dori-Darmon AJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>303333044</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000343586109001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2460,14 +2450,14 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №176/26</t>
+          <t>Оплата за товар по счет-фактуре №9043 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2477,38 +2467,38 @@
       </c>
       <c r="C57" s="2" t="n"/>
       <c r="D57" s="2" t="n">
-        <v>10535000</v>
+        <v>6877000</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Shartnoma №22/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9051</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2516,23 +2506,23 @@
           <t>148</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n">
-        <v>8541000</v>
-      </c>
-      <c r="D58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n">
+        <v>16371000</v>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sharq Dori-Darmon AJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>303333044</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000343586109001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2542,14 +2532,14 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №143/26</t>
+          <t>Shartnoma №72/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2559,38 +2549,38 @@
       </c>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n">
-        <v>7416000</v>
+        <v>106347000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Omad Sut MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>376718396</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000581419153001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4790 31.07.2026, QQS bilan</t>
+          <t>Shartnoma №150/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2599,34 +2589,39 @@
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>300000</v>
+        <v>62774000</v>
       </c>
       <c r="D60" s="2" t="n"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Namangan Meva Eksport XK</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Комиссия за перевод</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №266/26</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>15.08.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2635,39 +2630,34 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>66284000</v>
+        <v>17200000</v>
       </c>
       <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Angren Dori-Darmon AJ</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>284729090</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-3085)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000823744221001</t>
+          <t>16307000369122889417</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №106/26</t>
+          <t>Kredit shartnomasi L-2025-3085 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2677,38 +2667,38 @@
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n">
-        <v>13981000</v>
+        <v>15721000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Yangi Hayot Savdo MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>333044082</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000116267014001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, H/F №2617 03.08.2026, QQS BILAN</t>
+          <t>Mahsulot uchun to'lov, shartnoma №277/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2718,38 +2708,38 @@
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>2124000</v>
+        <v>8773000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Chust Tur Servis XK</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>272909008</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000374422121001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №245/26, QQS 12%</t>
+          <t>Shartnoma №36/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2757,40 +2747,40 @@
           <t>154</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n"/>
-      <c r="D64" s="2" t="n">
-        <v>1800000</v>
-      </c>
+      <c r="C64" s="2" t="n">
+        <v>2547000</v>
+      </c>
+      <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Oydin Sut MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>234114264</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000220906504001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3057</t>
+          <t>Iyul oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2798,40 +2788,40 @@
           <t>155</t>
         </is>
       </c>
-      <c r="C65" s="2" t="n"/>
-      <c r="D65" s="2" t="n">
-        <v>1415000</v>
-      </c>
+      <c r="C65" s="2" t="n">
+        <v>2547000</v>
+      </c>
+      <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>SHARTNOMA №163/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>JShDS iyul oyi uchun</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2839,40 +2829,40 @@
           <t>156</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="n">
-        <v>3085000</v>
-      </c>
+      <c r="C66" s="2" t="n">
+        <v>13132000</v>
+      </c>
+      <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Namangan Meva Eksport XK</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Shartnoma №286/26 bo'yicha oldindan to'lov</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №213/26</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2882,38 +2872,38 @@
       </c>
       <c r="C67" s="2" t="n"/>
       <c r="D67" s="2" t="n">
-        <v>3019000</v>
+        <v>22935000</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>SHARTNOMA №249/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Mahsulot uchun to'lov, shartnoma №76/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2922,34 +2912,39 @@
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>18677000</v>
+        <v>20768000</v>
       </c>
       <c r="D68" s="2" t="n"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Namangan Meva Eksport XK</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ish haqi, reestr №2192</t>
+          <t>Tovarlar uchun to'lov h/f №3609</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2959,38 +2954,38 @@
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>4202000</v>
+        <v>4114000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Chust Tur Servis XK</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>272909008</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000374422121001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №134/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №292/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2998,40 +2993,40 @@
           <t>160</t>
         </is>
       </c>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n">
-        <v>1672000</v>
-      </c>
+      <c r="C70" s="2" t="n">
+        <v>46008000</v>
+      </c>
+      <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Namangan Meva Eksport XK</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6511</t>
+          <t>Tovarlar uchun to'lov h/f №1948</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3039,23 +3034,23 @@
           <t>161</t>
         </is>
       </c>
-      <c r="C71" s="2" t="n">
-        <v>7651000</v>
-      </c>
-      <c r="D71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n">
+        <v>21894000</v>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sharq Dori-Darmon AJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>303333044</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000343586109001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3065,14 +3060,14 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №48/26</t>
+          <t>Shartnoma №125/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3082,38 +3077,38 @@
       </c>
       <c r="C72" s="2" t="n"/>
       <c r="D72" s="2" t="n">
-        <v>10932000</v>
+        <v>4565000</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Yangi Hayot Savdo MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>333044082</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000116267014001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7007</t>
+          <t>Shartnoma №98/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3123,38 +3118,38 @@
       </c>
       <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="n">
-        <v>3661000</v>
+        <v>4497000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Farg'ona Tikuv MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>204408221</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000626701482001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6965</t>
+          <t>SHARTNOMA №26/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3162,40 +3157,40 @@
           <t>164</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n">
-        <v>3375000</v>
-      </c>
+      <c r="C74" s="2" t="n">
+        <v>12222000</v>
+      </c>
+      <c r="D74" s="2" t="n"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Samarqand Savdo MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>348507161</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000861911625001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №138/26 от 10.08.2026</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №85/26</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3203,40 +3198,40 @@
           <t>165</t>
         </is>
       </c>
-      <c r="C75" s="2" t="n">
-        <v>2433000</v>
-      </c>
-      <c r="D75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n">
+        <v>7472000</v>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Farovon Qurilish MChJ</t>
+          <t>Farg'ona Tikuv MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>263920056</t>
+          <t>204408221</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000047556299001</t>
+          <t>20208000626701482001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Арендная плата за август 2026 г. по договору №43/22</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6169 24.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3244,40 +3239,40 @@
           <t>166</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n">
-        <v>2667000</v>
-      </c>
-      <c r="D76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n">
+        <v>6066000</v>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sharq Dori-Darmon AJ</t>
+          <t>Farg'ona Tikuv MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>303333044</t>
+          <t>204408221</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000343586109001</t>
+          <t>20208000626701482001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №125/26</t>
+          <t>Предоплта за товар по договору №69/26 от 24.08.2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3285,40 +3280,40 @@
           <t>167</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n">
-        <v>3589000</v>
-      </c>
-      <c r="D77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n">
+        <v>5929000</v>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sharq Dori-Darmon AJ</t>
+          <t>Chust Tur Servis XK</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>303333044</t>
+          <t>272909008</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000343586109001</t>
+          <t>20208000374422121001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8385</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №8977</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3328,38 +3323,38 @@
       </c>
       <c r="C78" s="2" t="n"/>
       <c r="D78" s="2" t="n">
-        <v>135414000</v>
+        <v>5840000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1486 от 12.08.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №118/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3367,40 +3362,40 @@
           <t>169</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n">
-        <v>15284000</v>
-      </c>
+      <c r="C79" s="2" t="n">
+        <v>4091000</v>
+      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Yangi Hayot Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>333044082</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000116267014001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2977 от 12.08.2026, в т.ч. НДС 12%</t>
+          <t>Уплата налога на добавленную стоимость за июль</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3408,40 +3403,40 @@
           <t>170</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n">
-        <v>2781000</v>
-      </c>
+      <c r="C80" s="2" t="n">
+        <v>1521000</v>
+      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Yangi Hayot Savdo MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>333044082</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000116267014001</t>
+          <t>20208000436392005001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5267</t>
+          <t>Elektr energiyasi uchun to'lov avgust</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3449,40 +3444,40 @@
           <t>171</t>
         </is>
       </c>
-      <c r="C81" s="2" t="n">
-        <v>2547000</v>
-      </c>
-      <c r="D81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n">
+        <v>5147000</v>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyul 2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6662 27.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3490,40 +3485,40 @@
           <t>172</t>
         </is>
       </c>
-      <c r="C82" s="2" t="n">
-        <v>2547000</v>
-      </c>
-      <c r="D82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n">
+        <v>3785000</v>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>НДФЛ за июль 2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3312 31.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3532,39 +3527,34 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>21209000</v>
+        <v>300000</v>
       </c>
       <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sharq Dori-Darmon AJ</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>303333044</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000343586109001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №143/26</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>15.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3573,17 +3563,22 @@
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>17200000</v>
+        <v>26140000</v>
       </c>
       <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-3085)</t>
+          <t>Nihol Yog' Zavodi AJ</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>331904146</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>16307000369122889417</t>
+          <t>20208000157846303001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3593,14 +3588,14 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-3085 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №4878</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3608,40 +3603,40 @@
           <t>175</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n"/>
-      <c r="D85" s="2" t="n">
-        <v>11995000</v>
-      </c>
+      <c r="C85" s="2" t="n">
+        <v>6217000</v>
+      </c>
+      <c r="D85" s="2" t="n"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Xiva Trans Servis AJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>359373150</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000258037213001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №36/26, НДС 12%</t>
+          <t>Предоплата за материалы по дог. №230/26</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3651,38 +3646,38 @@
       </c>
       <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="n">
-        <v>2383000</v>
+        <v>4392000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Andijon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>333470704</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000763103622001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №14/26, QQS 12%</t>
+          <t>Shartnoma №284/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,39 +3686,39 @@
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>221129000</v>
+        <v>2167000</v>
       </c>
       <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sharq Dori-Darmon AJ</t>
+          <t>Namangan Meva Eksport XK</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>303333044</t>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000343586109001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8447</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №188/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,38 +3728,38 @@
       </c>
       <c r="C88" s="2" t="n"/>
       <c r="D88" s="2" t="n">
-        <v>5555000</v>
+        <v>5661000</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Farg'ona Tikuv MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>204408221</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000626701482001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f 609</t>
+          <t>Shartnoma №19/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3774,38 +3769,38 @@
       </c>
       <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="n">
-        <v>1692000</v>
+        <v>3493000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Kamalak Sut Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>371839625</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000141915324001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №298/26, НДС 12%</t>
+          <t>Shartnoma №238/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3815,38 +3810,38 @@
       </c>
       <c r="C90" s="2" t="n"/>
       <c r="D90" s="2" t="n">
-        <v>3797000</v>
+        <v>2035000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kamalak Mato MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>294313691</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000272604074001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Shartnoma №92/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8694 7.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3855,39 +3850,39 @@
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>3954000</v>
+        <v>2673000</v>
       </c>
       <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Namangan Meva Eksport XK</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>QQS iyul 2026 uchun</t>
+          <t>Tovarlar uchun to'lov h/f №4167</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3895,40 +3890,35 @@
           <t>182</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n">
-        <v>16721000</v>
-      </c>
+      <c r="C92" s="2" t="n">
+        <v>19106000</v>
+      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Zafar Moy MChJ</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>233020938</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000661246275001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №795 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>Avgust oyi uchun ish haqi, reestr №9114</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3938,38 +3928,38 @@
       </c>
       <c r="C93" s="2" t="n"/>
       <c r="D93" s="2" t="n">
-        <v>5414000</v>
+        <v>26508000</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chust Tikuv MChJ</t>
+          <t>Kamalak Sut Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>365334707</t>
+          <t>371839625</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000447631036001</t>
+          <t>20208000141915324001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8743</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №770</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3977,40 +3967,40 @@
           <t>184</t>
         </is>
       </c>
-      <c r="C94" s="2" t="n"/>
-      <c r="D94" s="2" t="n">
-        <v>5130000</v>
-      </c>
+      <c r="C94" s="2" t="n">
+        <v>2489000</v>
+      </c>
+      <c r="D94" s="2" t="n"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Yangi Hayot Savdo MChJ</t>
+          <t>Namangan Qurilish XK</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>333044082</t>
+          <t>399761229</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000116267014001</t>
+          <t>20208000515269130001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №5118 ОТ 24.08.2026, В Т.Ч. НДС 12%</t>
+          <t>Арендапомещения за сентябрь, дог. №6/25</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4020,38 +4010,38 @@
       </c>
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="n">
-        <v>4534000</v>
+        <v>63054000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Yangi Hayot Savdo MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>333044082</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000116267014001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6098</t>
+          <t>Mahsulot uchun to'lov, shartn. №209/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4059,40 +4049,40 @@
           <t>186</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n">
-        <v>3415000</v>
-      </c>
+      <c r="C96" s="2" t="n">
+        <v>17232000</v>
+      </c>
+      <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Namangan Meva Eksport XK</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №160/26, QQS 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №268/26</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4102,38 +4092,38 @@
       </c>
       <c r="C97" s="2" t="n"/>
       <c r="D97" s="2" t="n">
-        <v>1475000</v>
+        <v>12385000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Oqtosh Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>202093836</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000124627509001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №263/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5363</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4142,39 +4132,39 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>3289000</v>
+        <v>9540000</v>
       </c>
       <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sharq Dori-Darmon AJ</t>
+          <t>Namangan Meva Eksport XK</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>303333044</t>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000343586109001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №291/26</t>
+          <t>Tovarlar uchun to'lov h/f №8503</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4184,38 +4174,38 @@
       </c>
       <c r="C99" s="2" t="n"/>
       <c r="D99" s="2" t="n">
-        <v>7804000</v>
+        <v>17098000</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Termiz Mebel MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>301825018</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000100195316001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №4972 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5080</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4223,40 +4213,40 @@
           <t>190</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n">
-        <v>2030000</v>
-      </c>
+      <c r="C100" s="2" t="n">
+        <v>2136000</v>
+      </c>
+      <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Termiz Mebel MChJ</t>
+          <t>Namangan Meva Eksport XK</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>301825018</t>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000100195316001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8315</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №170/26</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4264,40 +4254,40 @@
           <t>191</t>
         </is>
       </c>
-      <c r="C101" s="2" t="n"/>
-      <c r="D101" s="2" t="n">
-        <v>1682000</v>
-      </c>
+      <c r="C101" s="2" t="n">
+        <v>2160000</v>
+      </c>
+      <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Ilhom Qurilish MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>284133716</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000705592994001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №2251</t>
+          <t>Оплата за товары согласно с/ф №2738</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4305,40 +4295,35 @@
           <t>192</t>
         </is>
       </c>
-      <c r="C102" s="2" t="n"/>
-      <c r="D102" s="2" t="n">
-        <v>1946000</v>
-      </c>
+      <c r="C102" s="2" t="n">
+        <v>17200000</v>
+      </c>
+      <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Zafar Moy MChJ</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>233020938</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-3085)</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000661246275001</t>
+          <t>16307000369122889417</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №86/26, QQS 12%</t>
+          <t>Kredit shartnomasi L-2025-3085 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4346,40 +4331,40 @@
           <t>193</t>
         </is>
       </c>
-      <c r="C103" s="2" t="n">
-        <v>1521000</v>
-      </c>
-      <c r="D103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n">
+        <v>6814000</v>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000855050926001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №27/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4387,23 +4372,23 @@
           <t>194</t>
         </is>
       </c>
-      <c r="C104" s="2" t="n">
-        <v>22285000</v>
-      </c>
-      <c r="D104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n">
+        <v>4829000</v>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sharq Dori-Darmon AJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>303333044</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000343586109001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4413,14 +4398,14 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №45/26</t>
+          <t>Shartnoma №292/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4430,21 +4415,21 @@
       </c>
       <c r="C105" s="2" t="n"/>
       <c r="D105" s="2" t="n">
-        <v>2118000</v>
+        <v>2443000</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Dori-Darmon XK</t>
+          <t>Mehnat Tekstil MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>294858396</t>
+          <t>211426422</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000620259824001</t>
+          <t>20208000090650470001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4454,14 +4439,14 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №29/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2996</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4469,40 +4454,40 @@
           <t>196</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n">
-        <v>1486000</v>
-      </c>
+      <c r="C106" s="2" t="n">
+        <v>2605000</v>
+      </c>
+      <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8480</t>
+          <t>Ijtimoiy soliq avgust 2026</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4510,40 +4495,40 @@
           <t>197</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n"/>
-      <c r="D107" s="2" t="n">
-        <v>6612000</v>
-      </c>
+      <c r="C107" s="2" t="n">
+        <v>2605000</v>
+      </c>
+      <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8828</t>
+          <t>JShDS avgust oyi uchun</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4551,40 +4536,40 @@
           <t>198</t>
         </is>
       </c>
-      <c r="C108" s="2" t="n"/>
-      <c r="D108" s="2" t="n">
-        <v>4134000</v>
-      </c>
+      <c r="C108" s="2" t="n">
+        <v>3624000</v>
+      </c>
+      <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Namangan Meva Eksport XK</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2782 28.08.2026, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №111/26</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4594,38 +4579,38 @@
       </c>
       <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="n">
-        <v>15574000</v>
+        <v>2311000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2963 от 31.08.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2205</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4635,38 +4620,38 @@
       </c>
       <c r="C110" s="2" t="n"/>
       <c r="D110" s="2" t="n">
-        <v>9432000</v>
+        <v>2247000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Shartnoma №248/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №6324 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4674,40 +4659,40 @@
           <t>201</t>
         </is>
       </c>
-      <c r="C111" s="2" t="n"/>
-      <c r="D111" s="2" t="n">
-        <v>4121000</v>
-      </c>
+      <c r="C111" s="2" t="n">
+        <v>6459000</v>
+      </c>
+      <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Namangan Meva Eksport XK</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №3793 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №10/26</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4717,38 +4702,38 @@
       </c>
       <c r="C112" s="2" t="n"/>
       <c r="D112" s="2" t="n">
-        <v>3470000</v>
+        <v>4856000</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Andijon Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>333470704</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000763103622001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №3965</t>
+          <t>Shartnoma №295/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4758,38 +4743,38 @@
       </c>
       <c r="C113" s="2" t="n"/>
       <c r="D113" s="2" t="n">
-        <v>2440000</v>
+        <v>3129000</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №687 31.08.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №195/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4797,23 +4782,23 @@
           <t>204</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n">
-        <v>1835000</v>
-      </c>
+      <c r="C114" s="2" t="n">
+        <v>4121000</v>
+      </c>
+      <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Nihol Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>331904146</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000157846303001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4823,14 +4808,14 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №127/26, QQS 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №164/26</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4839,34 +4824,39 @@
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>300000</v>
+        <v>4216000</v>
       </c>
       <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4875,39 +4865,39 @@
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>5073000</v>
+        <v>6099000</v>
       </c>
       <c r="D116" s="2" t="n"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sharq Dori-Darmon AJ</t>
+          <t>Namangan Meva Eksport XK</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>303333044</t>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000343586109001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №290/26</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №25/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4915,40 +4905,40 @@
           <t>207</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n"/>
-      <c r="D117" s="2" t="n">
-        <v>12712000</v>
-      </c>
+      <c r="C117" s="2" t="n">
+        <v>6351000</v>
+      </c>
+      <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Namangan Meva Eksport XK</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №17/26 от 01.09.2026</t>
+          <t>Оплата за товары согласно счет-фактуре №2169</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4956,40 +4946,40 @@
           <t>208</t>
         </is>
       </c>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="2" t="n">
-        <v>7169000</v>
-      </c>
+      <c r="C118" s="2" t="n">
+        <v>8085000</v>
+      </c>
+      <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Namangan Meva Eksport XK</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №186/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartn. №17/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4999,38 +4989,38 @@
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>4428000</v>
+        <v>11093000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Chust Tikuv MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>365334707</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000447631036001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9201 02.09.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №5988 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5040,38 +5030,38 @@
       </c>
       <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="n">
-        <v>4005000</v>
+        <v>3323000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №277/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4440 25.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5079,40 +5069,40 @@
           <t>211</t>
         </is>
       </c>
-      <c r="C121" s="2" t="n"/>
-      <c r="D121" s="2" t="n">
-        <v>8448000</v>
-      </c>
+      <c r="C121" s="2" t="n">
+        <v>2916000</v>
+      </c>
+      <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Namangan Meva Eksport XK</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5289</t>
+          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №57/26</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5120,40 +5110,40 @@
           <t>212</t>
         </is>
       </c>
-      <c r="C122" s="2" t="n"/>
-      <c r="D122" s="2" t="n">
-        <v>3751000</v>
-      </c>
+      <c r="C122" s="2" t="n">
+        <v>5426000</v>
+      </c>
+      <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Zafar Moy MChJ</t>
+          <t>Namangan Meva Eksport XK</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>233020938</t>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000661246275001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Shartnoma №270/26 bo'yicha oldindan to'lov</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №175/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5161,40 +5151,40 @@
           <t>213</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n"/>
-      <c r="D123" s="2" t="n">
-        <v>24214000</v>
-      </c>
+      <c r="C123" s="2" t="n">
+        <v>179685000</v>
+      </c>
+      <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Namangan Meva Eksport XK</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Shartnoma №222/26 bo'yicha oldindan to'lov</t>
+          <t>Tovarlar uchun to'lov h/f №8734</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5204,38 +5194,38 @@
       </c>
       <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="n">
-        <v>18420000</v>
+        <v>3359000</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>284201097</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000995865816001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №218/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1122</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5243,40 +5233,40 @@
           <t>215</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n"/>
-      <c r="D125" s="2" t="n">
-        <v>13717000</v>
-      </c>
+      <c r="C125" s="2" t="n">
+        <v>1556000</v>
+      </c>
+      <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Chirchiq Mehmonxona AJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>271698862</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000686057103001</t>
+          <t>20208000436392005001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №7888</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5284,40 +5274,40 @@
           <t>216</t>
         </is>
       </c>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n">
-        <v>4550000</v>
-      </c>
+      <c r="C126" s="2" t="n">
+        <v>2406000</v>
+      </c>
+      <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Chust Tikuv MChJ</t>
+          <t>Namangan Meva Eksport XK</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>365334707</t>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000447631036001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6040 от 07.09.2026, в т.ч. НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №47/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5326,39 +5316,39 @@
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>8602000</v>
+        <v>2826000</v>
       </c>
       <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sharq Dori-Darmon AJ</t>
+          <t>Namangan Meva Eksport XK</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>303333044</t>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000343586109001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA№201/26</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №175/26</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5367,34 +5357,39 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>19106000</v>
+        <v>6098000</v>
       </c>
       <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Namangan Meva Eksport XK</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за август 2026 г. согласно реестру №2138</t>
+          <t>Tovarlar uchun to'lov h/f №1442</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>29.09.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5402,23 +5397,23 @@
           <t>219</t>
         </is>
       </c>
-      <c r="C129" s="2" t="n">
-        <v>57730000</v>
-      </c>
-      <c r="D129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n">
+        <v>172310000</v>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Mehnat Oziq-ovqat Savdo MChJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>264166099</t>
+          <t>220109759</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000374631289001</t>
+          <t>20208000586581621001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5428,14 +5423,14 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №259/26</t>
+          <t>Tovar uchun to'lov, h/f №3803 29.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5443,40 +5438,35 @@
           <t>220</t>
         </is>
       </c>
-      <c r="C130" s="2" t="n"/>
-      <c r="D130" s="2" t="n">
-        <v>7391000</v>
-      </c>
+      <c r="C130" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Oydin Sut MChJ</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>234114264</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000220906504001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5794</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5485,1852 +5475,58 @@
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>2489000</v>
+        <v>18108000</v>
       </c>
       <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Farovon Qurilish MChJ</t>
+          <t>Namangan Meva Eksport XK</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>263920056</t>
+          <t>216609983</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000047556299001</t>
+          <t>20208000463128958001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Ijara haqi sentyabr oyi uchun, shartnoma №43/22</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №225/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n">
-        <v>7619000</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>284201097</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>20208000995865816001</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по дог. №128/26 от 10.09.2026</t>
-        </is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="n">
+        <v>1013759000</v>
+      </c>
+      <c r="D132" s="4" t="n">
+        <v>1012759000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n">
-        <v>8667000</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Zafar Moy MChJ</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>233020938</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>20208000661246275001</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4642 11.09.2026, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>11.09.2026</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="n"/>
-      <c r="D134" s="2" t="n">
-        <v>3826000</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>284201097</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>20208000995865816001</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>Shartnoma №249/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="n"/>
-      <c r="D135" s="2" t="n">
-        <v>12701000</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Yangi Hayot Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>333044082</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>20208000116267014001</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №62/26, QQS 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="n"/>
-      <c r="D136" s="2" t="n">
-        <v>11068000</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Zafar Moy MChJ</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>233020938</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>20208000661246275001</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №5908 14.09.2026, QQS BILAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="n"/>
-      <c r="D137" s="2" t="n">
-        <v>3495000</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Yangi Hayot Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>333044082</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>20208000116267014001</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, h/f №1181 14.09.2026, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="n">
-        <v>2605000</v>
-      </c>
-      <c r="D138" s="2" t="n"/>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>Ijtimoiy soliq avgust 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="n">
-        <v>2605000</v>
-      </c>
-      <c r="D139" s="2" t="n"/>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>JShDS avgust oyi uchun</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="n">
-        <v>6377000</v>
-      </c>
-      <c r="D140" s="2" t="n"/>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Sharq Dori-Darmon AJ</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>303333044</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>20208000343586109001</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>Оплата за транспортные услуги по договору №270/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="n">
-        <v>12536000</v>
-      </c>
-      <c r="D141" s="2" t="n"/>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Mehnat Oziq-ovqat Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>264166099</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>20208000374631289001</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №134/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="n">
-        <v>54719000</v>
-      </c>
-      <c r="D142" s="2" t="n"/>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Marg'ilon Agro AJ</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>387593731</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>20208000002580372001</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>Tovarlar uchun to'lov h/f №5367</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>15.09.2026</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="n"/>
-      <c r="D143" s="2" t="n">
-        <v>60468000</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Termiz Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>301825018</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>20208000100195316001</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartn. №117/26, QQS 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>15.09.2026</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="n">
-        <v>17200000</v>
-      </c>
-      <c r="D144" s="2" t="n"/>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-3085)</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>16307000369122889417</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>Kredit shartnomasi L-2025-3085 bo'yicha navbatdagi to'lov (09.2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>17.09.2026</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n">
-        <v>3318000</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>284201097</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>20208000995865816001</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №49/26, QQS 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>17.09.2026</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="n">
-        <v>10341000</v>
-      </c>
-      <c r="D146" s="2" t="n"/>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Mehnat Oziq-ovqat Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>264166099</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>20208000374631289001</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №89/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>17.09.2026</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="n">
-        <v>16985000</v>
-      </c>
-      <c r="D147" s="2" t="n"/>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Angren Dori-Darmon AJ</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>284729090</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>20208000823744221001</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №288/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>18.09.2026</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="n"/>
-      <c r="D148" s="2" t="n">
-        <v>4321000</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Chust Tikuv MChJ</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>365334707</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>20208000447631036001</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, h/f №231 18.09.2026, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>18.09.2026</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="n">
-        <v>8537000</v>
-      </c>
-      <c r="D149" s="2" t="n"/>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Zafar Tikuv MChJ</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>359976122</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>20208000651526913001</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Tovarlar uchun to'lov h/f №2131</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>18.09.2026</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="n">
-        <v>22474000</v>
-      </c>
-      <c r="D150" s="2" t="n"/>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Sharq Dori-Darmon AJ</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>303333044</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>20208000343586109001</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>Tovarlar uchun to'lov h/f №3328</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="n"/>
-      <c r="D151" s="2" t="n">
-        <v>9044000</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Shodlik Sut AJ</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>222328820</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>20208000000669864001</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №283/26, QQS 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="n"/>
-      <c r="D152" s="2" t="n">
-        <v>6356000</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>284201097</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>20208000995865816001</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartn. №167/26, QQS 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="n"/>
-      <c r="D153" s="2" t="n">
-        <v>6346000</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Zafar Moy MChJ</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>233020938</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>20208000661246275001</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №488</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>22.09.2026</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="n"/>
-      <c r="D154" s="2" t="n">
-        <v>18248000</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>284201097</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>20208000995865816001</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2043 22.09.2026, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>22.09.2026</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="n"/>
-      <c r="D155" s="2" t="n">
-        <v>4299000</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>284201097</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>20208000995865816001</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisobfaktura №3251 22.09.2026, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>22.09.2026</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="n"/>
-      <c r="D156" s="2" t="n">
-        <v>4072000</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>284201097</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>20208000995865816001</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2471 22.09.2026, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>22.09.2026</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="n">
-        <v>4153000</v>
-      </c>
-      <c r="D157" s="2" t="n"/>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>QO'SHILGAN QIYMAT SOLIG'I AVGUST OYI</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>22.09.2026</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="n">
-        <v>20475000</v>
-      </c>
-      <c r="D158" s="2" t="n"/>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Sharq Dori-Darmon AJ</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>303333044</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>20208000343586109001</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Xom ashyo uchun to'ov, shartnoma №252/26, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>23.09.2026</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="n"/>
-      <c r="D159" s="2" t="n">
-        <v>7484000</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Yangi Hayot Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>333044082</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>20208000116267014001</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3386</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>23.09.2026</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="n"/>
-      <c r="D160" s="2" t="n">
-        <v>7245000</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Yangi Hayot Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>333044082</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>20208000116267014001</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №161/26, QQS 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>23.09.2026</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="n">
-        <v>6752000</v>
-      </c>
-      <c r="D161" s="2" t="n"/>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Sharq Dori-Darmon AJ</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>303333044</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>20208000343586109001</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №163/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>25.09.2026</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="n"/>
-      <c r="D162" s="2" t="n">
-        <v>12488000</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Yangi Hayot Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>333044082</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>20208000116267014001</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7494 25.09.2026, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>25.09.2026</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="n"/>
-      <c r="D163" s="2" t="n">
-        <v>7620000</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Yangi Hayot Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>333044082</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>20208000116267014001</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №9824 за поставленный товар</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>25.09.2026</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="n">
-        <v>13641000</v>
-      </c>
-      <c r="D164" s="2" t="n"/>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Mehnat Oziq-ovqat Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>264166099</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>20208000374631289001</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №130/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="n"/>
-      <c r="D165" s="2" t="n">
-        <v>9066000</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>284201097</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>20208000995865816001</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Shartnoma №172/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="n"/>
-      <c r="D166" s="2" t="n">
-        <v>6367000</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Kamalak Mato MChJ</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>294313691</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>20208000272604074001</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Shartnoma №14/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="n"/>
-      <c r="D167" s="2" t="n">
-        <v>4315000</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>284201097</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>20208000995865816001</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №250/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="n">
-        <v>1556000</v>
-      </c>
-      <c r="D168" s="2" t="n"/>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>200933985</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>20208000855050926001</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>Elektr energiyasi uchun to'lov</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="n">
-        <v>11919000</v>
-      </c>
-      <c r="D169" s="2" t="n"/>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Angren Dori-Darmon AJ</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>284729090</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>20208000823744221001</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTN. №17/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="n">
-        <v>14891000</v>
-      </c>
-      <c r="D170" s="2" t="n"/>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Mehnat Oziq-ovqat Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>264166099</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>20208000374631289001</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>Оплата за транспортные услуги по договору №179/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="n">
-        <v>22157000</v>
-      </c>
-      <c r="D171" s="2" t="n"/>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Sharq Dori-Darmon AJ</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>303333044</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>20208000343586109001</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №47/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="n"/>
-      <c r="D172" s="2" t="n">
-        <v>7709000</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>284201097</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>20208000995865816001</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №297/26, QQS 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="n"/>
-      <c r="D173" s="2" t="n">
-        <v>7747000</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>284201097</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>20208000995865816001</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №159/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="n"/>
-      <c r="D174" s="2" t="n">
-        <v>3387000</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Lazzat Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>284201097</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>20208000995865816001</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>Shartnoma №208/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D175" s="2" t="n"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Bodomzor Bank ATB</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>Комиссия за перевод</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C176" s="4" t="n">
-        <v>995298000</v>
-      </c>
-      <c r="D176" s="4" t="n">
-        <v>994298000</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C177" s="4" t="n">
+      <c r="C133" s="4" t="n">
         <v>36500000</v>
       </c>
-      <c r="D177" s="4" t="n"/>
+      <c r="D133" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
